--- a/artfynd/A 40322-2024 artfynd.xlsx
+++ b/artfynd/A 40322-2024 artfynd.xlsx
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">

--- a/artfynd/A 40322-2024 artfynd.xlsx
+++ b/artfynd/A 40322-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66500231</v>
+        <v>86292476</v>
       </c>
       <c r="B2" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Messlingen S, Hjd</t>
+          <t>Messlingen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>386570.8207708354</v>
+        <v>386204</v>
       </c>
       <c r="R2" t="n">
-        <v>6950866.151976799</v>
+        <v>6950923</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-08-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-08-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,38 +757,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>13367</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66500237</v>
+        <v>66500231</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386672.9457869269</v>
+        <v>386571</v>
       </c>
       <c r="R3" t="n">
-        <v>6950769.298932069</v>
+        <v>6950866</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,26 +844,11 @@
           <t>2011-08-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-08-17</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>hackspår</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -896,7 +860,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>13367</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>77022500</v>
+        <v>77022553</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386318.8813813905</v>
+        <v>386296</v>
       </c>
       <c r="R4" t="n">
-        <v>6950770.895074613</v>
+        <v>6950835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,26 +949,16 @@
           <t>2019-04-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-04-13</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
@@ -1030,15 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>77022540</v>
+        <v>86292548</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,17 +1013,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>N Kappruet, Hjd</t>
+          <t>Messlingen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386296.22701975</v>
+        <v>386468</v>
       </c>
       <c r="R5" t="n">
-        <v>6950835.132783816</v>
+        <v>6950603</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,22 +1047,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-04-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-04-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,27 +1068,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>77022666</v>
+        <v>86386955</v>
       </c>
       <c r="B6" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,37 +1091,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>N Kappruet, Hjd</t>
+          <t>Kappruet Östra, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386585.9277611672</v>
+        <v>386169</v>
       </c>
       <c r="R6" t="n">
-        <v>6950555.236073736</v>
+        <v>6950841</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,22 +1145,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-04-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-04-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,7 +1159,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1262,37 +1177,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>77022553</v>
+        <v>86292508</v>
       </c>
       <c r="B7" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>310</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,17 +1211,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>N Kappruet, Hjd</t>
+          <t>Messlingen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386296.22701975</v>
+        <v>386346</v>
       </c>
       <c r="R7" t="n">
-        <v>6950835.132783816</v>
+        <v>6950804</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,29 +1245,19 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-04-13</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-04-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
@@ -1366,27 +1266,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>77022658</v>
+        <v>77022540</v>
       </c>
       <c r="B8" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1421,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>386585.9277611672</v>
+        <v>386296</v>
       </c>
       <c r="R8" t="n">
-        <v>6950555.236073736</v>
+        <v>6950835</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,19 +1349,9 @@
           <t>2019-04-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-04-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,37 +1379,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>77022478</v>
+        <v>86292657</v>
       </c>
       <c r="B9" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1533,17 +1413,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Kappruet, Hjd</t>
+          <t>Messlingen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>386355.9520098126</v>
+        <v>386587</v>
       </c>
       <c r="R9" t="n">
-        <v>6950724.094210429</v>
+        <v>6950518</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,22 +1447,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-04-13</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-04-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,27 +1468,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>77022752</v>
+        <v>115378577</v>
       </c>
       <c r="B10" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,37 +1491,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>N Kappruet, Hjd</t>
+          <t>Kappruet Östra, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>386493.1218975568</v>
+        <v>386202</v>
       </c>
       <c r="R10" t="n">
-        <v>6950668.791980728</v>
+        <v>6950796</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,22 +1545,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-04-13</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-04-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,7 +1559,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1726,54 +1577,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>77022627</v>
+        <v>86386951</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Kappruet, Hjd</t>
+          <t>Kappruet Östra, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>386568.1440067035</v>
+        <v>386194</v>
       </c>
       <c r="R11" t="n">
-        <v>6950573.781815124</v>
+        <v>6950784</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,27 +1642,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-04-13</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-04-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2020-06-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,15 +1674,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>86292534</v>
+        <v>77022516</v>
       </c>
       <c r="B12" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,21 +1685,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1886,17 +1708,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Messlingen, Hjd</t>
+          <t>N Kappruet, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386411.1219689567</v>
+        <v>386189</v>
       </c>
       <c r="R12" t="n">
-        <v>6950667.93321625</v>
+        <v>6950921</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1920,22 +1742,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-04-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-04-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,27 +1763,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>86292637</v>
+        <v>77022666</v>
       </c>
       <c r="B13" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,21 +1786,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2002,17 +1809,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Messlingen, Hjd</t>
+          <t>N Kappruet, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>386580.2004818548</v>
+        <v>386586</v>
       </c>
       <c r="R13" t="n">
-        <v>6950562.790698128</v>
+        <v>6950555</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2036,22 +1843,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-04-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-04-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,49 +1864,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>86292657</v>
+        <v>77022468</v>
       </c>
       <c r="B14" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2118,17 +1910,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Messlingen, Hjd</t>
+          <t>N Kappruet, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>386586.9497029858</v>
+        <v>386188</v>
       </c>
       <c r="R14" t="n">
-        <v>6950517.951394415</v>
+        <v>6950909</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2152,22 +1944,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-04-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-04-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,27 +1965,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>86292611</v>
+        <v>77022478</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,41 +1988,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Messlingen, Hjd</t>
+          <t>N Kappruet, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>386564.8926079936</v>
+        <v>386356</v>
       </c>
       <c r="R15" t="n">
-        <v>6950572.973784872</v>
+        <v>6950724</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2269,27 +2045,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-04-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2019-04-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2298,33 +2059,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>86292591</v>
+        <v>86292534</v>
       </c>
       <c r="B16" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,21 +2089,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2359,10 +2116,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>386509.8985097664</v>
+        <v>386411</v>
       </c>
       <c r="R16" t="n">
-        <v>6950594.177957989</v>
+        <v>6950668</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2392,19 +2149,9 @@
           <t>2020-06-13</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2432,37 +2179,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>86292508</v>
+        <v>86292660</v>
       </c>
       <c r="B17" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2475,10 +2217,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>386345.808600858</v>
+        <v>386587</v>
       </c>
       <c r="R17" t="n">
-        <v>6950803.996108269</v>
+        <v>6950518</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2508,19 +2250,9 @@
           <t>2020-06-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2548,56 +2280,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>86292660</v>
+        <v>66500237</v>
       </c>
       <c r="B18" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Messlingen, Hjd</t>
+          <t>Messlingen S, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>386586.9497029858</v>
+        <v>386673</v>
       </c>
       <c r="R18" t="n">
-        <v>6950517.951394415</v>
+        <v>6950769</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2621,22 +2345,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-08-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-08-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>hackspår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2645,34 +2364,33 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>13372</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>86292548</v>
+        <v>77022627</v>
       </c>
       <c r="B19" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2680,40 +2398,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Messlingen, Hjd</t>
+          <t>N Kappruet, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>386467.8336054849</v>
+        <v>386568</v>
       </c>
       <c r="R19" t="n">
-        <v>6950602.981932264</v>
+        <v>6950574</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2737,22 +2456,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-04-13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-04-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2761,34 +2475,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>86386949</v>
+        <v>86292611</v>
       </c>
       <c r="B20" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2796,37 +2504,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kappruet Östra, Hjd</t>
+          <t>Messlingen, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>386204.815623745</v>
+        <v>386565</v>
       </c>
       <c r="R20" t="n">
-        <v>6950748.15368674</v>
+        <v>6950573</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2853,19 +2565,14 @@
           <t>2020-06-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2020-06-13</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2880,27 +2587,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>86386950</v>
+        <v>115378352</v>
       </c>
       <c r="B21" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2908,34 +2610,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kappruet Östra, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>386207.7811365117</v>
+        <v>386227</v>
       </c>
       <c r="R21" t="n">
-        <v>6950754.029469918</v>
+        <v>6950744</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2962,22 +2669,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3004,15 +2701,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>86386948</v>
+        <v>115378521</v>
       </c>
       <c r="B22" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3020,34 +2712,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kappruet Östra, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>386198.994550495</v>
+        <v>386223</v>
       </c>
       <c r="R22" t="n">
-        <v>6950752.9527861</v>
+        <v>6950711</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3074,22 +2771,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3116,53 +2803,56 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>86386953</v>
+        <v>86292645</v>
       </c>
       <c r="B23" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kappruet Östra, Hjd</t>
+          <t>Messlingen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>386182.9896833393</v>
+        <v>386579</v>
       </c>
       <c r="R23" t="n">
-        <v>6950782.934486882</v>
+        <v>6950561</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3189,19 +2879,9 @@
           <t>2020-06-13</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3216,27 +2896,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>86386951</v>
+        <v>86386954</v>
       </c>
       <c r="B24" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80398</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3244,21 +2919,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>229748</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3268,10 +2943,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>386194.0759373597</v>
+        <v>386166</v>
       </c>
       <c r="R24" t="n">
-        <v>6950783.931840452</v>
+        <v>6950827</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3301,19 +2976,9 @@
           <t>2020-06-13</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2020-06-13</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3340,15 +3005,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115378577</v>
+        <v>77022658</v>
       </c>
       <c r="B25" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,34 +3016,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kappruet Östra, Hjd</t>
+          <t>N Kappruet, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>386202</v>
+        <v>386586</v>
       </c>
       <c r="R25" t="n">
-        <v>6950796</v>
+        <v>6950555</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3410,12 +3073,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2019-04-13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2019-04-13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3424,6 +3087,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3442,15 +3106,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115378521</v>
+        <v>86292637</v>
       </c>
       <c r="B26" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3458,42 +3117,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kappruet Östra, Hjd</t>
+          <t>Messlingen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>386223</v>
+        <v>386580</v>
       </c>
       <c r="R26" t="n">
-        <v>6950711</v>
+        <v>6950563</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3517,12 +3174,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-06-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2020-06-13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3531,128 +3188,22 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>115378352</v>
-      </c>
-      <c r="B27" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Kappruet Östra, Hjd</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>386227</v>
-      </c>
-      <c r="R27" t="n">
-        <v>6950744</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2024-03-24</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2024-03-24</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40322-2024 artfynd.xlsx
+++ b/artfynd/A 40322-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86292476</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66500231</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77022553</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86292548</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1174,6 +1199,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86386955</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1275,6 +1305,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86292508</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77022540</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1477,6 +1517,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86292657</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1574,6 +1619,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115378577</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1671,6 +1721,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86386951</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1772,6 +1827,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77022516</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1873,6 +1933,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77022666</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1974,6 +2039,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77022468</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2075,6 +2145,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77022478</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2176,6 +2251,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86292534</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2277,6 +2357,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86292660</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2384,6 +2469,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66500237</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77022627</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2596,6 +2691,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86292611</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2698,6 +2798,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115378352</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2800,6 +2905,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115378521</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2905,6 +3015,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86292645</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3002,6 +3117,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86386954</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3103,6 +3223,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77022658</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3204,8 +3329,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86292637</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>